--- a/Executive_Capstone_Report/AMEX_RiskIQ_Platform_Executive_Capstone_Workbook.xlsx
+++ b/Executive_Capstone_Report/AMEX_RiskIQ_Platform_Executive_Capstone_Workbook.xlsx
@@ -10,7 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Executive Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Problem Registry" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Financial Summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Category Breakdown" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Financial Methodology" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Category Breakdown" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0.00"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,8 +53,20 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <color rgb="005A6373"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000B1F3A"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -85,6 +98,11 @@
         <fgColor rgb="00C9A227"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FBF3DC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -112,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -130,6 +148,21 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -208,7 +241,6 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -1710,6 +1742,115 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Financial Methodology -- What Is Measured vs. What Is Assumed</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="62" customHeight="1">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>The Kaggle American Express Default Prediction dataset this entire platform is built on is deliberately anonymized: it contains no revenue, credit-limit, exposure, or loss-recovery columns, by the competition's own design. Every dollar figure in this workbook is therefore built from two clearly separated ingredients, and this platform never blends the two without saying which is which.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Measured, from the real data</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>Every predicted default probability, population count, and true/false-positive and true/false-negative outcome count in this workbook is computed live by that problem's own trained model against real, held-out customers -- fully reproducible by re-running the platform's own notebooks against the same dataset.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Assumed, where the dataset has no ground truth</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>Exposure-at-default, loss-given-default, revenue-per-account, and every treatment cost used in a net-benefit calculation are explicitly labeled ASSUMPTION values, sourced from commonly-cited unsecured-retail credit industry benchmarks -- never invented silently and never presented as if the dataset itself provided them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>Every net-benefit figure is the product of the two</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>Real population counts and real model outcomes, multiplied by assumption-labeled dollar values per outcome. No dollar total anywhere in this workbook is read directly from a data column, because no such column exists in the raw dataset.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>Full traceability, not a hidden constant</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>All 10 of this platform's financial_assumptions.json files -- one per value-creation problem -- log the exact value, its source, and a documented rationale for every assumption used, each explicitly marked "edit to your institution's actual figures."</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>The revenue proxy, specifically (Problem 13)</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>Built from the dataset's own real "S_" (Spend) feature columns -- real and genuinely present, though anonymized -- converted into a real per-customer spend percentile rank, then scaled by an assumption-labeled average revenue figure. Reported explicitly as a revenue proxy, never as audited revenue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="62" customHeight="1">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>What this means for the $429,926,252.73 total</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>It is a transparent, fully-documented methodology applied to real model outputs and stated financial assumptions -- not a number American Express, or any institution, has realized. Every assumption is designed to be replaced with an institution's own real unit economics to produce that institution's own real total.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C7"/>
